--- a/src/data/ideal_ilce_genisletilmis.son.xlsx
+++ b/src/data/ideal_ilce_genisletilmis.son.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmet\OneDrive\Masaüstü\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB301064-5408-4C99-9F2D-E76E203115FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEAF3DFE-89C2-4F4B-90FE-BC235FD7D4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4596" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="districts_app" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="864">
   <si>
     <t>district_id</t>
   </si>
@@ -2070,6 +2070,390 @@
   </si>
   <si>
     <t>Çanakkale / Lapseki</t>
+  </si>
+  <si>
+    <t>manisa-sehzadeler</t>
+  </si>
+  <si>
+    <t>Şehzadeler</t>
+  </si>
+  <si>
+    <t>Manisa / Şehzadeler</t>
+  </si>
+  <si>
+    <t>manisa-turgutlu</t>
+  </si>
+  <si>
+    <t>Turgutlu</t>
+  </si>
+  <si>
+    <t>Manisa / Turgutlu</t>
+  </si>
+  <si>
+    <t>manisa-salihli</t>
+  </si>
+  <si>
+    <t>Salihli</t>
+  </si>
+  <si>
+    <t>Manisa / Salihli</t>
+  </si>
+  <si>
+    <t>manisa-akhisar</t>
+  </si>
+  <si>
+    <t>Akhisar</t>
+  </si>
+  <si>
+    <t>Manisa / Akhisar</t>
+  </si>
+  <si>
+    <t>manisa-soma</t>
+  </si>
+  <si>
+    <t>Soma</t>
+  </si>
+  <si>
+    <t>Manisa / Soma</t>
+  </si>
+  <si>
+    <t>manisa-alasehir</t>
+  </si>
+  <si>
+    <t>Alaşehir</t>
+  </si>
+  <si>
+    <t>Manisa / Alaşehir</t>
+  </si>
+  <si>
+    <t>eskisehir-sivrihisar</t>
+  </si>
+  <si>
+    <t>Sivrihisar</t>
+  </si>
+  <si>
+    <t>Eskişehir / Sivrihisar</t>
+  </si>
+  <si>
+    <t>eskisehir-mihalgazi</t>
+  </si>
+  <si>
+    <t>Mihalgazi</t>
+  </si>
+  <si>
+    <t>Eskişehir / Mihalgazi</t>
+  </si>
+  <si>
+    <t>eskisehir-mahmudiye</t>
+  </si>
+  <si>
+    <t>Mahmudiye</t>
+  </si>
+  <si>
+    <t>Eskişehir / Mahmudiye</t>
+  </si>
+  <si>
+    <t>antalya-serik</t>
+  </si>
+  <si>
+    <t>Serik</t>
+  </si>
+  <si>
+    <t>Antalya / Serik</t>
+  </si>
+  <si>
+    <t>antalya-kaş</t>
+  </si>
+  <si>
+    <t>Kaş</t>
+  </si>
+  <si>
+    <t>Antalya / Kaş</t>
+  </si>
+  <si>
+    <t>antalya-finike</t>
+  </si>
+  <si>
+    <t>Finike</t>
+  </si>
+  <si>
+    <t>Antalya / Finike</t>
+  </si>
+  <si>
+    <t>antalya-gazipasa</t>
+  </si>
+  <si>
+    <t>Gazipaşa</t>
+  </si>
+  <si>
+    <t>Antalya / Gazipaşa</t>
+  </si>
+  <si>
+    <t>antalya-kumluca</t>
+  </si>
+  <si>
+    <t>Kumluca</t>
+  </si>
+  <si>
+    <t>Antalya / Kumluca</t>
+  </si>
+  <si>
+    <t>antalya-elmali</t>
+  </si>
+  <si>
+    <t>Elmalı</t>
+  </si>
+  <si>
+    <t>Antalya / Elmalı</t>
+  </si>
+  <si>
+    <t>antalya-akseki</t>
+  </si>
+  <si>
+    <t>Akseki</t>
+  </si>
+  <si>
+    <t>Antalya / Akseki</t>
+  </si>
+  <si>
+    <t>antalya-ibradı</t>
+  </si>
+  <si>
+    <t>İbradı</t>
+  </si>
+  <si>
+    <t>Antalya / İbradı</t>
+  </si>
+  <si>
+    <t>malatya-yesilyurt</t>
+  </si>
+  <si>
+    <t>Yeşilyurt</t>
+  </si>
+  <si>
+    <t>Malatya / Yeşilyurt</t>
+  </si>
+  <si>
+    <t>malatya-dogansehir</t>
+  </si>
+  <si>
+    <t>Doğanşehir</t>
+  </si>
+  <si>
+    <t>Malatya / Doğanşehir</t>
+  </si>
+  <si>
+    <t>elazig-kovancılar</t>
+  </si>
+  <si>
+    <t>Kovancılar</t>
+  </si>
+  <si>
+    <t>Elazığ / Kovancılar</t>
+  </si>
+  <si>
+    <t>diyarbakir-baglar</t>
+  </si>
+  <si>
+    <t>Bağlar</t>
+  </si>
+  <si>
+    <t>Diyarbakır / Bağlar</t>
+  </si>
+  <si>
+    <t>diyarbakir-yenisehir</t>
+  </si>
+  <si>
+    <t>Diyarbakır / Yenişehir</t>
+  </si>
+  <si>
+    <t>diyarbakir-sur</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
+    <t>Diyarbakır / Sur</t>
+  </si>
+  <si>
+    <t>sanliurfa-haliliye</t>
+  </si>
+  <si>
+    <t>Haliliye</t>
+  </si>
+  <si>
+    <t>Şanlıurfa / Haliliye</t>
+  </si>
+  <si>
+    <t>sanliurfa-eyupnebi</t>
+  </si>
+  <si>
+    <t>Eyyübiye</t>
+  </si>
+  <si>
+    <t>Şanlıurfa / Eyyübiye</t>
+  </si>
+  <si>
+    <t>van-tusba</t>
+  </si>
+  <si>
+    <t>Tuşba</t>
+  </si>
+  <si>
+    <t>Van / Tuşba</t>
+  </si>
+  <si>
+    <t>erzurum-palandoken</t>
+  </si>
+  <si>
+    <t>Palandöken</t>
+  </si>
+  <si>
+    <t>Erzurum / Palandöken</t>
+  </si>
+  <si>
+    <t>erzurum-aziziye</t>
+  </si>
+  <si>
+    <t>Aziziye</t>
+  </si>
+  <si>
+    <t>Erzurum / Aziziye</t>
+  </si>
+  <si>
+    <t>gaziantep-sahinbey</t>
+  </si>
+  <si>
+    <t>Şahinbey</t>
+  </si>
+  <si>
+    <t>Gaziantep / Şahinbey</t>
+  </si>
+  <si>
+    <t>TRC1 Kuzeydoğu Akdeniz</t>
+  </si>
+  <si>
+    <t>gaziantep-nizip</t>
+  </si>
+  <si>
+    <t>Nizip</t>
+  </si>
+  <si>
+    <t>Gaziantep / Nizip</t>
+  </si>
+  <si>
+    <t>gaziantep-islahiye</t>
+  </si>
+  <si>
+    <t>İslahiye</t>
+  </si>
+  <si>
+    <t>Gaziantep / İslahiye</t>
+  </si>
+  <si>
+    <t>kahramanmaras-dulkadiroglу</t>
+  </si>
+  <si>
+    <t>Dulkadiroğlu</t>
+  </si>
+  <si>
+    <t>Kahramanmaraş / Dulkadiroğlu</t>
+  </si>
+  <si>
+    <t>kahramanmaras-elbistan</t>
+  </si>
+  <si>
+    <t>Elbistan</t>
+  </si>
+  <si>
+    <t>Kahramanmaraş / Elbistan</t>
+  </si>
+  <si>
+    <t>hatay-iskenderun</t>
+  </si>
+  <si>
+    <t>İskenderun</t>
+  </si>
+  <si>
+    <t>Hatay / İskenderun</t>
+  </si>
+  <si>
+    <t>hatay-samandag</t>
+  </si>
+  <si>
+    <t>Samandağ</t>
+  </si>
+  <si>
+    <t>Hatay / Samandağ</t>
+  </si>
+  <si>
+    <t>hatay-dortyol</t>
+  </si>
+  <si>
+    <t>Dörtyol</t>
+  </si>
+  <si>
+    <t>Hatay / Dörtyol</t>
+  </si>
+  <si>
+    <t>hatay-kirikhan</t>
+  </si>
+  <si>
+    <t>Kırıkhan</t>
+  </si>
+  <si>
+    <t>Hatay / Kırıkhan</t>
+  </si>
+  <si>
+    <t>hatay-reyhanli</t>
+  </si>
+  <si>
+    <t>Reyhanlı</t>
+  </si>
+  <si>
+    <t>Hatay / Reyhanlı</t>
+  </si>
+  <si>
+    <t>adiyaman-merkez</t>
+  </si>
+  <si>
+    <t>Adıyaman</t>
+  </si>
+  <si>
+    <t>Adıyaman / Merkez</t>
+  </si>
+  <si>
+    <t>adiyaman-golbasi</t>
+  </si>
+  <si>
+    <t>Adıyaman / Gölbaşı</t>
+  </si>
+  <si>
+    <t>mardin-kiziltepe</t>
+  </si>
+  <si>
+    <t>Kızıltepe</t>
+  </si>
+  <si>
+    <t>Mardin / Kızıltepe</t>
+  </si>
+  <si>
+    <t>mardin-midyat</t>
+  </si>
+  <si>
+    <t>Midyat</t>
+  </si>
+  <si>
+    <t>Mardin / Midyat</t>
+  </si>
+  <si>
+    <t>mardin-nusaybin</t>
+  </si>
+  <si>
+    <t>Nusaybin</t>
+  </si>
+  <si>
+    <t>Mardin / Nusaybin</t>
   </si>
   <si>
     <t>metric_key</t>
@@ -2567,7 +2951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD187"/>
+  <dimension ref="A1:AD230"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -18478,6 +18862,3317 @@
       </c>
       <c r="AD187">
         <v>26.683299999999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:30">
+      <c r="A188" t="s">
+        <v>678</v>
+      </c>
+      <c r="B188" t="s">
+        <v>349</v>
+      </c>
+      <c r="C188" t="s">
+        <v>679</v>
+      </c>
+      <c r="D188" t="s">
+        <v>680</v>
+      </c>
+      <c r="E188">
+        <v>44.9</v>
+      </c>
+      <c r="J188">
+        <v>250000</v>
+      </c>
+      <c r="K188">
+        <v>1.4</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188" t="s">
+        <v>407</v>
+      </c>
+      <c r="N188">
+        <v>9</v>
+      </c>
+      <c r="O188" t="s">
+        <v>54</v>
+      </c>
+      <c r="P188">
+        <v>15</v>
+      </c>
+      <c r="Q188">
+        <v>11</v>
+      </c>
+      <c r="R188" t="s">
+        <v>70</v>
+      </c>
+      <c r="S188">
+        <v>17.5</v>
+      </c>
+      <c r="T188" t="s">
+        <v>408</v>
+      </c>
+      <c r="U188">
+        <v>18000</v>
+      </c>
+      <c r="V188">
+        <v>112</v>
+      </c>
+      <c r="W188">
+        <v>12200</v>
+      </c>
+      <c r="X188">
+        <v>2300000</v>
+      </c>
+      <c r="Y188">
+        <v>20.5</v>
+      </c>
+      <c r="Z188">
+        <v>15</v>
+      </c>
+      <c r="AB188" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC188">
+        <v>38.616700000000002</v>
+      </c>
+      <c r="AD188">
+        <v>27.433299999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:30">
+      <c r="A189" t="s">
+        <v>681</v>
+      </c>
+      <c r="B189" t="s">
+        <v>349</v>
+      </c>
+      <c r="C189" t="s">
+        <v>682</v>
+      </c>
+      <c r="D189" t="s">
+        <v>683</v>
+      </c>
+      <c r="E189">
+        <v>47</v>
+      </c>
+      <c r="J189">
+        <v>145000</v>
+      </c>
+      <c r="K189">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189" t="s">
+        <v>407</v>
+      </c>
+      <c r="N189">
+        <v>10</v>
+      </c>
+      <c r="O189" t="s">
+        <v>61</v>
+      </c>
+      <c r="P189">
+        <v>16</v>
+      </c>
+      <c r="Q189">
+        <v>11.5</v>
+      </c>
+      <c r="R189" t="s">
+        <v>70</v>
+      </c>
+      <c r="S189">
+        <v>17.8</v>
+      </c>
+      <c r="T189" t="s">
+        <v>408</v>
+      </c>
+      <c r="U189">
+        <v>16500</v>
+      </c>
+      <c r="V189">
+        <v>103</v>
+      </c>
+      <c r="W189">
+        <v>11200</v>
+      </c>
+      <c r="X189">
+        <v>2100000</v>
+      </c>
+      <c r="Y189">
+        <v>19</v>
+      </c>
+      <c r="Z189">
+        <v>15</v>
+      </c>
+      <c r="AB189" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC189">
+        <v>38.5</v>
+      </c>
+      <c r="AD189">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:30">
+      <c r="A190" t="s">
+        <v>684</v>
+      </c>
+      <c r="B190" t="s">
+        <v>349</v>
+      </c>
+      <c r="C190" t="s">
+        <v>685</v>
+      </c>
+      <c r="D190" t="s">
+        <v>686</v>
+      </c>
+      <c r="E190">
+        <v>47.5</v>
+      </c>
+      <c r="J190">
+        <v>130000</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190" t="s">
+        <v>407</v>
+      </c>
+      <c r="N190">
+        <v>10</v>
+      </c>
+      <c r="O190" t="s">
+        <v>61</v>
+      </c>
+      <c r="P190">
+        <v>17</v>
+      </c>
+      <c r="Q190">
+        <v>11</v>
+      </c>
+      <c r="R190" t="s">
+        <v>70</v>
+      </c>
+      <c r="S190">
+        <v>18</v>
+      </c>
+      <c r="T190" t="s">
+        <v>408</v>
+      </c>
+      <c r="U190">
+        <v>15500</v>
+      </c>
+      <c r="V190">
+        <v>97</v>
+      </c>
+      <c r="W190">
+        <v>10500</v>
+      </c>
+      <c r="X190">
+        <v>1950000</v>
+      </c>
+      <c r="Y190">
+        <v>18.5</v>
+      </c>
+      <c r="Z190">
+        <v>15</v>
+      </c>
+      <c r="AB190" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC190">
+        <v>38.4833</v>
+      </c>
+      <c r="AD190">
+        <v>28.133299999999998</v>
+      </c>
+    </row>
+    <row r="191" spans="1:30">
+      <c r="A191" t="s">
+        <v>687</v>
+      </c>
+      <c r="B191" t="s">
+        <v>349</v>
+      </c>
+      <c r="C191" t="s">
+        <v>688</v>
+      </c>
+      <c r="D191" t="s">
+        <v>689</v>
+      </c>
+      <c r="E191">
+        <v>47.9</v>
+      </c>
+      <c r="J191">
+        <v>130000</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191" t="s">
+        <v>407</v>
+      </c>
+      <c r="N191">
+        <v>10</v>
+      </c>
+      <c r="O191" t="s">
+        <v>61</v>
+      </c>
+      <c r="P191">
+        <v>17</v>
+      </c>
+      <c r="Q191">
+        <v>11.5</v>
+      </c>
+      <c r="R191" t="s">
+        <v>70</v>
+      </c>
+      <c r="S191">
+        <v>18</v>
+      </c>
+      <c r="T191" t="s">
+        <v>408</v>
+      </c>
+      <c r="U191">
+        <v>15000</v>
+      </c>
+      <c r="V191">
+        <v>94</v>
+      </c>
+      <c r="W191">
+        <v>10200</v>
+      </c>
+      <c r="X191">
+        <v>1900000</v>
+      </c>
+      <c r="Y191">
+        <v>18</v>
+      </c>
+      <c r="Z191">
+        <v>15</v>
+      </c>
+      <c r="AB191" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC191">
+        <v>38.916699999999999</v>
+      </c>
+      <c r="AD191">
+        <v>27.833300000000001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:30">
+      <c r="A192" t="s">
+        <v>690</v>
+      </c>
+      <c r="B192" t="s">
+        <v>349</v>
+      </c>
+      <c r="C192" t="s">
+        <v>691</v>
+      </c>
+      <c r="D192" t="s">
+        <v>692</v>
+      </c>
+      <c r="E192">
+        <v>48.4</v>
+      </c>
+      <c r="J192">
+        <v>90000</v>
+      </c>
+      <c r="K192">
+        <v>0.9</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192" t="s">
+        <v>407</v>
+      </c>
+      <c r="N192">
+        <v>11</v>
+      </c>
+      <c r="O192" t="s">
+        <v>77</v>
+      </c>
+      <c r="P192">
+        <v>17</v>
+      </c>
+      <c r="Q192">
+        <v>11</v>
+      </c>
+      <c r="R192" t="s">
+        <v>70</v>
+      </c>
+      <c r="S192">
+        <v>18.2</v>
+      </c>
+      <c r="T192" t="s">
+        <v>408</v>
+      </c>
+      <c r="U192">
+        <v>13500</v>
+      </c>
+      <c r="V192">
+        <v>87</v>
+      </c>
+      <c r="W192">
+        <v>9500</v>
+      </c>
+      <c r="X192">
+        <v>1700000</v>
+      </c>
+      <c r="Y192">
+        <v>17.5</v>
+      </c>
+      <c r="Z192">
+        <v>15</v>
+      </c>
+      <c r="AB192" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC192">
+        <v>39.183300000000003</v>
+      </c>
+      <c r="AD192">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:30">
+      <c r="A193" t="s">
+        <v>693</v>
+      </c>
+      <c r="B193" t="s">
+        <v>349</v>
+      </c>
+      <c r="C193" t="s">
+        <v>694</v>
+      </c>
+      <c r="D193" t="s">
+        <v>695</v>
+      </c>
+      <c r="E193">
+        <v>47.6</v>
+      </c>
+      <c r="J193">
+        <v>80000</v>
+      </c>
+      <c r="K193">
+        <v>0.9</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193" t="s">
+        <v>407</v>
+      </c>
+      <c r="N193">
+        <v>10</v>
+      </c>
+      <c r="O193" t="s">
+        <v>61</v>
+      </c>
+      <c r="P193">
+        <v>17</v>
+      </c>
+      <c r="Q193">
+        <v>11</v>
+      </c>
+      <c r="R193" t="s">
+        <v>70</v>
+      </c>
+      <c r="S193">
+        <v>18.2</v>
+      </c>
+      <c r="T193" t="s">
+        <v>408</v>
+      </c>
+      <c r="U193">
+        <v>14000</v>
+      </c>
+      <c r="V193">
+        <v>88</v>
+      </c>
+      <c r="W193">
+        <v>9600</v>
+      </c>
+      <c r="X193">
+        <v>1750000</v>
+      </c>
+      <c r="Y193">
+        <v>17.8</v>
+      </c>
+      <c r="Z193">
+        <v>15</v>
+      </c>
+      <c r="AB193" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC193">
+        <v>38.35</v>
+      </c>
+      <c r="AD193">
+        <v>28.5167</v>
+      </c>
+    </row>
+    <row r="194" spans="1:30">
+      <c r="A194" t="s">
+        <v>696</v>
+      </c>
+      <c r="B194" t="s">
+        <v>291</v>
+      </c>
+      <c r="C194" t="s">
+        <v>697</v>
+      </c>
+      <c r="D194" t="s">
+        <v>698</v>
+      </c>
+      <c r="E194">
+        <v>54.1</v>
+      </c>
+      <c r="J194">
+        <v>25000</v>
+      </c>
+      <c r="K194">
+        <v>0.6</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194" t="s">
+        <v>407</v>
+      </c>
+      <c r="N194">
+        <v>15</v>
+      </c>
+      <c r="O194" t="s">
+        <v>35</v>
+      </c>
+      <c r="P194">
+        <v>19</v>
+      </c>
+      <c r="Q194">
+        <v>11.5</v>
+      </c>
+      <c r="R194" t="s">
+        <v>207</v>
+      </c>
+      <c r="S194">
+        <v>18.8</v>
+      </c>
+      <c r="T194" t="s">
+        <v>408</v>
+      </c>
+      <c r="U194">
+        <v>11000</v>
+      </c>
+      <c r="V194">
+        <v>72</v>
+      </c>
+      <c r="W194">
+        <v>8000</v>
+      </c>
+      <c r="X194">
+        <v>1400000</v>
+      </c>
+      <c r="Y194">
+        <v>16</v>
+      </c>
+      <c r="Z194">
+        <v>14</v>
+      </c>
+      <c r="AB194" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC194">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="AD194">
+        <v>31.533300000000001</v>
+      </c>
+    </row>
+    <row r="195" spans="1:30">
+      <c r="A195" t="s">
+        <v>699</v>
+      </c>
+      <c r="B195" t="s">
+        <v>291</v>
+      </c>
+      <c r="C195" t="s">
+        <v>700</v>
+      </c>
+      <c r="D195" t="s">
+        <v>701</v>
+      </c>
+      <c r="E195">
+        <v>55.4</v>
+      </c>
+      <c r="J195">
+        <v>10000</v>
+      </c>
+      <c r="K195">
+        <v>0.5</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195" t="s">
+        <v>407</v>
+      </c>
+      <c r="N195">
+        <v>15</v>
+      </c>
+      <c r="O195" t="s">
+        <v>35</v>
+      </c>
+      <c r="P195">
+        <v>20</v>
+      </c>
+      <c r="Q195">
+        <v>12</v>
+      </c>
+      <c r="R195" t="s">
+        <v>207</v>
+      </c>
+      <c r="S195">
+        <v>19</v>
+      </c>
+      <c r="T195" t="s">
+        <v>408</v>
+      </c>
+      <c r="U195">
+        <v>9500</v>
+      </c>
+      <c r="V195">
+        <v>62</v>
+      </c>
+      <c r="W195">
+        <v>7000</v>
+      </c>
+      <c r="X195">
+        <v>1200000</v>
+      </c>
+      <c r="Y195">
+        <v>15</v>
+      </c>
+      <c r="Z195">
+        <v>14</v>
+      </c>
+      <c r="AB195" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC195">
+        <v>40.0167</v>
+      </c>
+      <c r="AD195">
+        <v>30.566700000000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:30">
+      <c r="A196" t="s">
+        <v>702</v>
+      </c>
+      <c r="B196" t="s">
+        <v>291</v>
+      </c>
+      <c r="C196" t="s">
+        <v>703</v>
+      </c>
+      <c r="D196" t="s">
+        <v>704</v>
+      </c>
+      <c r="E196">
+        <v>53.6</v>
+      </c>
+      <c r="J196">
+        <v>20000</v>
+      </c>
+      <c r="K196">
+        <v>0.5</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196" t="s">
+        <v>407</v>
+      </c>
+      <c r="N196">
+        <v>14</v>
+      </c>
+      <c r="O196" t="s">
+        <v>77</v>
+      </c>
+      <c r="P196">
+        <v>19</v>
+      </c>
+      <c r="Q196">
+        <v>12</v>
+      </c>
+      <c r="R196" t="s">
+        <v>207</v>
+      </c>
+      <c r="S196">
+        <v>18.8</v>
+      </c>
+      <c r="T196" t="s">
+        <v>408</v>
+      </c>
+      <c r="U196">
+        <v>10000</v>
+      </c>
+      <c r="V196">
+        <v>65</v>
+      </c>
+      <c r="W196">
+        <v>7200</v>
+      </c>
+      <c r="X196">
+        <v>1250000</v>
+      </c>
+      <c r="Y196">
+        <v>15.5</v>
+      </c>
+      <c r="Z196">
+        <v>14</v>
+      </c>
+      <c r="AB196" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC196">
+        <v>39.6</v>
+      </c>
+      <c r="AD196">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="197" spans="1:30">
+      <c r="A197" t="s">
+        <v>705</v>
+      </c>
+      <c r="B197" t="s">
+        <v>91</v>
+      </c>
+      <c r="C197" t="s">
+        <v>706</v>
+      </c>
+      <c r="D197" t="s">
+        <v>707</v>
+      </c>
+      <c r="E197">
+        <v>56.8</v>
+      </c>
+      <c r="J197">
+        <v>130000</v>
+      </c>
+      <c r="K197">
+        <v>1.2</v>
+      </c>
+      <c r="L197">
+        <v>14</v>
+      </c>
+      <c r="M197" t="s">
+        <v>34</v>
+      </c>
+      <c r="N197">
+        <v>8</v>
+      </c>
+      <c r="O197" t="s">
+        <v>54</v>
+      </c>
+      <c r="P197">
+        <v>17</v>
+      </c>
+      <c r="Q197">
+        <v>11.5</v>
+      </c>
+      <c r="R197" t="s">
+        <v>78</v>
+      </c>
+      <c r="S197">
+        <v>16.5</v>
+      </c>
+      <c r="T197" t="s">
+        <v>408</v>
+      </c>
+      <c r="U197">
+        <v>28000</v>
+      </c>
+      <c r="V197">
+        <v>168</v>
+      </c>
+      <c r="W197">
+        <v>17500</v>
+      </c>
+      <c r="X197">
+        <v>3600000</v>
+      </c>
+      <c r="Y197">
+        <v>24.5</v>
+      </c>
+      <c r="Z197">
+        <v>17</v>
+      </c>
+      <c r="AB197" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC197">
+        <v>36.916699999999999</v>
+      </c>
+      <c r="AD197">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:30">
+      <c r="A198" t="s">
+        <v>708</v>
+      </c>
+      <c r="B198" t="s">
+        <v>91</v>
+      </c>
+      <c r="C198" t="s">
+        <v>709</v>
+      </c>
+      <c r="D198" t="s">
+        <v>710</v>
+      </c>
+      <c r="E198">
+        <v>63.5</v>
+      </c>
+      <c r="J198">
+        <v>30000</v>
+      </c>
+      <c r="K198">
+        <v>1.2</v>
+      </c>
+      <c r="L198">
+        <v>20</v>
+      </c>
+      <c r="M198" t="s">
+        <v>34</v>
+      </c>
+      <c r="N198">
+        <v>9</v>
+      </c>
+      <c r="O198" t="s">
+        <v>54</v>
+      </c>
+      <c r="P198">
+        <v>19</v>
+      </c>
+      <c r="Q198">
+        <v>12.5</v>
+      </c>
+      <c r="R198" t="s">
+        <v>78</v>
+      </c>
+      <c r="S198">
+        <v>14.5</v>
+      </c>
+      <c r="T198" t="s">
+        <v>408</v>
+      </c>
+      <c r="U198">
+        <v>65000</v>
+      </c>
+      <c r="V198">
+        <v>320</v>
+      </c>
+      <c r="W198">
+        <v>28000</v>
+      </c>
+      <c r="X198">
+        <v>8500000</v>
+      </c>
+      <c r="Y198">
+        <v>32</v>
+      </c>
+      <c r="Z198">
+        <v>22</v>
+      </c>
+      <c r="AB198" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC198">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="AD198">
+        <v>29.633299999999998</v>
+      </c>
+    </row>
+    <row r="199" spans="1:30">
+      <c r="A199" t="s">
+        <v>711</v>
+      </c>
+      <c r="B199" t="s">
+        <v>91</v>
+      </c>
+      <c r="C199" t="s">
+        <v>712</v>
+      </c>
+      <c r="D199" t="s">
+        <v>713</v>
+      </c>
+      <c r="E199">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="J199">
+        <v>30000</v>
+      </c>
+      <c r="K199">
+        <v>0.9</v>
+      </c>
+      <c r="L199">
+        <v>20</v>
+      </c>
+      <c r="M199" t="s">
+        <v>34</v>
+      </c>
+      <c r="N199">
+        <v>9</v>
+      </c>
+      <c r="O199" t="s">
+        <v>54</v>
+      </c>
+      <c r="P199">
+        <v>19</v>
+      </c>
+      <c r="Q199">
+        <v>12</v>
+      </c>
+      <c r="R199" t="s">
+        <v>78</v>
+      </c>
+      <c r="S199">
+        <v>16</v>
+      </c>
+      <c r="T199" t="s">
+        <v>408</v>
+      </c>
+      <c r="U199">
+        <v>30000</v>
+      </c>
+      <c r="V199">
+        <v>178</v>
+      </c>
+      <c r="W199">
+        <v>18500</v>
+      </c>
+      <c r="X199">
+        <v>3900000</v>
+      </c>
+      <c r="Y199">
+        <v>25</v>
+      </c>
+      <c r="Z199">
+        <v>18</v>
+      </c>
+      <c r="AB199" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC199">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="AD199">
+        <v>30.15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:30">
+      <c r="A200" t="s">
+        <v>714</v>
+      </c>
+      <c r="B200" t="s">
+        <v>91</v>
+      </c>
+      <c r="C200" t="s">
+        <v>715</v>
+      </c>
+      <c r="D200" t="s">
+        <v>716</v>
+      </c>
+      <c r="E200">
+        <v>60.1</v>
+      </c>
+      <c r="J200">
+        <v>50000</v>
+      </c>
+      <c r="K200">
+        <v>0.8</v>
+      </c>
+      <c r="L200">
+        <v>16</v>
+      </c>
+      <c r="M200" t="s">
+        <v>34</v>
+      </c>
+      <c r="N200">
+        <v>9</v>
+      </c>
+      <c r="O200" t="s">
+        <v>54</v>
+      </c>
+      <c r="P200">
+        <v>18</v>
+      </c>
+      <c r="Q200">
+        <v>11.5</v>
+      </c>
+      <c r="R200" t="s">
+        <v>78</v>
+      </c>
+      <c r="S200">
+        <v>16.8</v>
+      </c>
+      <c r="T200" t="s">
+        <v>408</v>
+      </c>
+      <c r="U200">
+        <v>22000</v>
+      </c>
+      <c r="V200">
+        <v>135</v>
+      </c>
+      <c r="W200">
+        <v>14500</v>
+      </c>
+      <c r="X200">
+        <v>2800000</v>
+      </c>
+      <c r="Y200">
+        <v>22</v>
+      </c>
+      <c r="Z200">
+        <v>16</v>
+      </c>
+      <c r="AB200" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC200">
+        <v>36.2667</v>
+      </c>
+      <c r="AD200">
+        <v>32.316699999999997</v>
+      </c>
+    </row>
+    <row r="201" spans="1:30">
+      <c r="A201" t="s">
+        <v>717</v>
+      </c>
+      <c r="B201" t="s">
+        <v>91</v>
+      </c>
+      <c r="C201" t="s">
+        <v>718</v>
+      </c>
+      <c r="D201" t="s">
+        <v>719</v>
+      </c>
+      <c r="E201">
+        <v>58.4</v>
+      </c>
+      <c r="J201">
+        <v>55000</v>
+      </c>
+      <c r="K201">
+        <v>0.8</v>
+      </c>
+      <c r="L201">
+        <v>14</v>
+      </c>
+      <c r="M201" t="s">
+        <v>34</v>
+      </c>
+      <c r="N201">
+        <v>9</v>
+      </c>
+      <c r="O201" t="s">
+        <v>54</v>
+      </c>
+      <c r="P201">
+        <v>18</v>
+      </c>
+      <c r="Q201">
+        <v>11.5</v>
+      </c>
+      <c r="R201" t="s">
+        <v>78</v>
+      </c>
+      <c r="S201">
+        <v>16.8</v>
+      </c>
+      <c r="T201" t="s">
+        <v>408</v>
+      </c>
+      <c r="U201">
+        <v>22000</v>
+      </c>
+      <c r="V201">
+        <v>133</v>
+      </c>
+      <c r="W201">
+        <v>14200</v>
+      </c>
+      <c r="X201">
+        <v>2800000</v>
+      </c>
+      <c r="Y201">
+        <v>21.5</v>
+      </c>
+      <c r="Z201">
+        <v>16</v>
+      </c>
+      <c r="AB201" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC201">
+        <v>36.366700000000002</v>
+      </c>
+      <c r="AD201">
+        <v>30.283300000000001</v>
+      </c>
+    </row>
+    <row r="202" spans="1:30">
+      <c r="A202" t="s">
+        <v>720</v>
+      </c>
+      <c r="B202" t="s">
+        <v>91</v>
+      </c>
+      <c r="C202" t="s">
+        <v>721</v>
+      </c>
+      <c r="D202" t="s">
+        <v>722</v>
+      </c>
+      <c r="E202">
+        <v>51.8</v>
+      </c>
+      <c r="J202">
+        <v>40000</v>
+      </c>
+      <c r="K202">
+        <v>0.7</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202" t="s">
+        <v>407</v>
+      </c>
+      <c r="N202">
+        <v>12</v>
+      </c>
+      <c r="O202" t="s">
+        <v>77</v>
+      </c>
+      <c r="P202">
+        <v>19</v>
+      </c>
+      <c r="Q202">
+        <v>12</v>
+      </c>
+      <c r="R202" t="s">
+        <v>78</v>
+      </c>
+      <c r="S202">
+        <v>18.5</v>
+      </c>
+      <c r="T202" t="s">
+        <v>408</v>
+      </c>
+      <c r="U202">
+        <v>13000</v>
+      </c>
+      <c r="V202">
+        <v>85</v>
+      </c>
+      <c r="W202">
+        <v>9400</v>
+      </c>
+      <c r="X202">
+        <v>1650000</v>
+      </c>
+      <c r="Y202">
+        <v>17.5</v>
+      </c>
+      <c r="Z202">
+        <v>15</v>
+      </c>
+      <c r="AB202" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC202">
+        <v>36.7333</v>
+      </c>
+      <c r="AD202">
+        <v>29.916699999999999</v>
+      </c>
+    </row>
+    <row r="203" spans="1:30">
+      <c r="A203" t="s">
+        <v>723</v>
+      </c>
+      <c r="B203" t="s">
+        <v>91</v>
+      </c>
+      <c r="C203" t="s">
+        <v>724</v>
+      </c>
+      <c r="D203" t="s">
+        <v>725</v>
+      </c>
+      <c r="E203">
+        <v>54.2</v>
+      </c>
+      <c r="J203">
+        <v>15000</v>
+      </c>
+      <c r="K203">
+        <v>0.5</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203" t="s">
+        <v>407</v>
+      </c>
+      <c r="N203">
+        <v>13</v>
+      </c>
+      <c r="O203" t="s">
+        <v>77</v>
+      </c>
+      <c r="P203">
+        <v>20</v>
+      </c>
+      <c r="Q203">
+        <v>12.5</v>
+      </c>
+      <c r="R203" t="s">
+        <v>78</v>
+      </c>
+      <c r="S203">
+        <v>19</v>
+      </c>
+      <c r="T203" t="s">
+        <v>408</v>
+      </c>
+      <c r="U203">
+        <v>10500</v>
+      </c>
+      <c r="V203">
+        <v>68</v>
+      </c>
+      <c r="W203">
+        <v>7600</v>
+      </c>
+      <c r="X203">
+        <v>1300000</v>
+      </c>
+      <c r="Y203">
+        <v>16</v>
+      </c>
+      <c r="Z203">
+        <v>14</v>
+      </c>
+      <c r="AB203" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC203">
+        <v>37.049999999999997</v>
+      </c>
+      <c r="AD203">
+        <v>31.783300000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:30">
+      <c r="A204" t="s">
+        <v>726</v>
+      </c>
+      <c r="B204" t="s">
+        <v>91</v>
+      </c>
+      <c r="C204" t="s">
+        <v>727</v>
+      </c>
+      <c r="D204" t="s">
+        <v>728</v>
+      </c>
+      <c r="E204">
+        <v>54.9</v>
+      </c>
+      <c r="J204">
+        <v>5000</v>
+      </c>
+      <c r="K204">
+        <v>0.4</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204" t="s">
+        <v>407</v>
+      </c>
+      <c r="N204">
+        <v>13</v>
+      </c>
+      <c r="O204" t="s">
+        <v>77</v>
+      </c>
+      <c r="P204">
+        <v>20</v>
+      </c>
+      <c r="Q204">
+        <v>13</v>
+      </c>
+      <c r="R204" t="s">
+        <v>78</v>
+      </c>
+      <c r="S204">
+        <v>19.5</v>
+      </c>
+      <c r="T204" t="s">
+        <v>408</v>
+      </c>
+      <c r="U204">
+        <v>9000</v>
+      </c>
+      <c r="V204">
+        <v>58</v>
+      </c>
+      <c r="W204">
+        <v>6500</v>
+      </c>
+      <c r="X204">
+        <v>1100000</v>
+      </c>
+      <c r="Y204">
+        <v>15</v>
+      </c>
+      <c r="Z204">
+        <v>14</v>
+      </c>
+      <c r="AB204" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC204">
+        <v>37.15</v>
+      </c>
+      <c r="AD204">
+        <v>31.566700000000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:30">
+      <c r="A205" t="s">
+        <v>729</v>
+      </c>
+      <c r="B205" t="s">
+        <v>502</v>
+      </c>
+      <c r="C205" t="s">
+        <v>730</v>
+      </c>
+      <c r="D205" t="s">
+        <v>731</v>
+      </c>
+      <c r="E205">
+        <v>43.9</v>
+      </c>
+      <c r="J205">
+        <v>250000</v>
+      </c>
+      <c r="K205">
+        <v>1.2</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205" t="s">
+        <v>407</v>
+      </c>
+      <c r="N205">
+        <v>8</v>
+      </c>
+      <c r="O205" t="s">
+        <v>54</v>
+      </c>
+      <c r="P205">
+        <v>15</v>
+      </c>
+      <c r="Q205">
+        <v>10</v>
+      </c>
+      <c r="R205" t="s">
+        <v>458</v>
+      </c>
+      <c r="S205">
+        <v>18.5</v>
+      </c>
+      <c r="T205" t="s">
+        <v>408</v>
+      </c>
+      <c r="U205">
+        <v>14000</v>
+      </c>
+      <c r="V205">
+        <v>92</v>
+      </c>
+      <c r="W205">
+        <v>10200</v>
+      </c>
+      <c r="X205">
+        <v>1800000</v>
+      </c>
+      <c r="Y205">
+        <v>18</v>
+      </c>
+      <c r="Z205">
+        <v>15</v>
+      </c>
+      <c r="AB205" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC205">
+        <v>38.366700000000002</v>
+      </c>
+      <c r="AD205">
+        <v>38.283299999999997</v>
+      </c>
+    </row>
+    <row r="206" spans="1:30">
+      <c r="A206" t="s">
+        <v>732</v>
+      </c>
+      <c r="B206" t="s">
+        <v>502</v>
+      </c>
+      <c r="C206" t="s">
+        <v>733</v>
+      </c>
+      <c r="D206" t="s">
+        <v>734</v>
+      </c>
+      <c r="E206">
+        <v>47.4</v>
+      </c>
+      <c r="J206">
+        <v>35000</v>
+      </c>
+      <c r="K206">
+        <v>0.6</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206" t="s">
+        <v>407</v>
+      </c>
+      <c r="N206">
+        <v>9</v>
+      </c>
+      <c r="O206" t="s">
+        <v>54</v>
+      </c>
+      <c r="P206">
+        <v>18</v>
+      </c>
+      <c r="Q206">
+        <v>10.5</v>
+      </c>
+      <c r="R206" t="s">
+        <v>458</v>
+      </c>
+      <c r="S206">
+        <v>18.8</v>
+      </c>
+      <c r="T206" t="s">
+        <v>408</v>
+      </c>
+      <c r="U206">
+        <v>10500</v>
+      </c>
+      <c r="V206">
+        <v>68</v>
+      </c>
+      <c r="W206">
+        <v>7500</v>
+      </c>
+      <c r="X206">
+        <v>1250000</v>
+      </c>
+      <c r="Y206">
+        <v>15.5</v>
+      </c>
+      <c r="Z206">
+        <v>14</v>
+      </c>
+      <c r="AB206" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC206">
+        <v>38.1</v>
+      </c>
+      <c r="AD206">
+        <v>37.883299999999998</v>
+      </c>
+    </row>
+    <row r="207" spans="1:30">
+      <c r="A207" t="s">
+        <v>735</v>
+      </c>
+      <c r="B207" t="s">
+        <v>456</v>
+      </c>
+      <c r="C207" t="s">
+        <v>736</v>
+      </c>
+      <c r="D207" t="s">
+        <v>737</v>
+      </c>
+      <c r="E207">
+        <v>46.8</v>
+      </c>
+      <c r="J207">
+        <v>55000</v>
+      </c>
+      <c r="K207">
+        <v>0.8</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207" t="s">
+        <v>407</v>
+      </c>
+      <c r="N207">
+        <v>10</v>
+      </c>
+      <c r="O207" t="s">
+        <v>61</v>
+      </c>
+      <c r="P207">
+        <v>17</v>
+      </c>
+      <c r="Q207">
+        <v>9.5</v>
+      </c>
+      <c r="R207" t="s">
+        <v>458</v>
+      </c>
+      <c r="S207">
+        <v>18.8</v>
+      </c>
+      <c r="T207" t="s">
+        <v>408</v>
+      </c>
+      <c r="U207">
+        <v>10500</v>
+      </c>
+      <c r="V207">
+        <v>68</v>
+      </c>
+      <c r="W207">
+        <v>7500</v>
+      </c>
+      <c r="X207">
+        <v>1250000</v>
+      </c>
+      <c r="Y207">
+        <v>15</v>
+      </c>
+      <c r="Z207">
+        <v>14</v>
+      </c>
+      <c r="AB207" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC207">
+        <v>38.716700000000003</v>
+      </c>
+      <c r="AD207">
+        <v>39.833300000000001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:30">
+      <c r="A208" t="s">
+        <v>738</v>
+      </c>
+      <c r="B208" t="s">
+        <v>450</v>
+      </c>
+      <c r="C208" t="s">
+        <v>739</v>
+      </c>
+      <c r="D208" t="s">
+        <v>740</v>
+      </c>
+      <c r="E208">
+        <v>43.7</v>
+      </c>
+      <c r="J208">
+        <v>450000</v>
+      </c>
+      <c r="K208">
+        <v>0.9</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208" t="s">
+        <v>407</v>
+      </c>
+      <c r="N208">
+        <v>15</v>
+      </c>
+      <c r="O208" t="s">
+        <v>44</v>
+      </c>
+      <c r="P208">
+        <v>11</v>
+      </c>
+      <c r="Q208">
+        <v>7</v>
+      </c>
+      <c r="R208" t="s">
+        <v>413</v>
+      </c>
+      <c r="S208">
+        <v>18.5</v>
+      </c>
+      <c r="T208" t="s">
+        <v>408</v>
+      </c>
+      <c r="U208">
+        <v>11000</v>
+      </c>
+      <c r="V208">
+        <v>70</v>
+      </c>
+      <c r="W208">
+        <v>7800</v>
+      </c>
+      <c r="X208">
+        <v>1350000</v>
+      </c>
+      <c r="Y208">
+        <v>15.5</v>
+      </c>
+      <c r="Z208">
+        <v>14</v>
+      </c>
+      <c r="AB208" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC208">
+        <v>37.933300000000003</v>
+      </c>
+      <c r="AD208">
+        <v>40.216700000000003</v>
+      </c>
+    </row>
+    <row r="209" spans="1:30">
+      <c r="A209" t="s">
+        <v>741</v>
+      </c>
+      <c r="B209" t="s">
+        <v>450</v>
+      </c>
+      <c r="C209" t="s">
+        <v>75</v>
+      </c>
+      <c r="D209" t="s">
+        <v>742</v>
+      </c>
+      <c r="E209">
+        <v>45.6</v>
+      </c>
+      <c r="J209">
+        <v>200000</v>
+      </c>
+      <c r="K209">
+        <v>1.2</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209" t="s">
+        <v>407</v>
+      </c>
+      <c r="N209">
+        <v>15</v>
+      </c>
+      <c r="O209" t="s">
+        <v>44</v>
+      </c>
+      <c r="P209">
+        <v>13</v>
+      </c>
+      <c r="Q209">
+        <v>7.5</v>
+      </c>
+      <c r="R209" t="s">
+        <v>413</v>
+      </c>
+      <c r="S209">
+        <v>18</v>
+      </c>
+      <c r="T209" t="s">
+        <v>408</v>
+      </c>
+      <c r="U209">
+        <v>13000</v>
+      </c>
+      <c r="V209">
+        <v>83</v>
+      </c>
+      <c r="W209">
+        <v>9200</v>
+      </c>
+      <c r="X209">
+        <v>1650000</v>
+      </c>
+      <c r="Y209">
+        <v>16.5</v>
+      </c>
+      <c r="Z209">
+        <v>15</v>
+      </c>
+      <c r="AB209" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC209">
+        <v>37.9</v>
+      </c>
+      <c r="AD209">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:30">
+      <c r="A210" t="s">
+        <v>743</v>
+      </c>
+      <c r="B210" t="s">
+        <v>450</v>
+      </c>
+      <c r="C210" t="s">
+        <v>744</v>
+      </c>
+      <c r="D210" t="s">
+        <v>745</v>
+      </c>
+      <c r="E210">
+        <v>46.1</v>
+      </c>
+      <c r="J210">
+        <v>100000</v>
+      </c>
+      <c r="K210">
+        <v>0.8</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210" t="s">
+        <v>407</v>
+      </c>
+      <c r="N210">
+        <v>15</v>
+      </c>
+      <c r="O210" t="s">
+        <v>44</v>
+      </c>
+      <c r="P210">
+        <v>14</v>
+      </c>
+      <c r="Q210">
+        <v>7</v>
+      </c>
+      <c r="R210" t="s">
+        <v>413</v>
+      </c>
+      <c r="S210">
+        <v>18.5</v>
+      </c>
+      <c r="T210" t="s">
+        <v>408</v>
+      </c>
+      <c r="U210">
+        <v>10500</v>
+      </c>
+      <c r="V210">
+        <v>67</v>
+      </c>
+      <c r="W210">
+        <v>7400</v>
+      </c>
+      <c r="X210">
+        <v>1250000</v>
+      </c>
+      <c r="Y210">
+        <v>15</v>
+      </c>
+      <c r="Z210">
+        <v>14</v>
+      </c>
+      <c r="AB210" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC210">
+        <v>37.916699999999999</v>
+      </c>
+      <c r="AD210">
+        <v>40.2333</v>
+      </c>
+    </row>
+    <row r="211" spans="1:30">
+      <c r="A211" t="s">
+        <v>746</v>
+      </c>
+      <c r="B211" t="s">
+        <v>532</v>
+      </c>
+      <c r="C211" t="s">
+        <v>747</v>
+      </c>
+      <c r="D211" t="s">
+        <v>748</v>
+      </c>
+      <c r="E211">
+        <v>44.8</v>
+      </c>
+      <c r="J211">
+        <v>400000</v>
+      </c>
+      <c r="K211">
+        <v>0.8</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211" t="s">
+        <v>407</v>
+      </c>
+      <c r="N211">
+        <v>15</v>
+      </c>
+      <c r="O211" t="s">
+        <v>44</v>
+      </c>
+      <c r="P211">
+        <v>12</v>
+      </c>
+      <c r="Q211">
+        <v>7</v>
+      </c>
+      <c r="R211" t="s">
+        <v>413</v>
+      </c>
+      <c r="S211">
+        <v>19</v>
+      </c>
+      <c r="T211" t="s">
+        <v>408</v>
+      </c>
+      <c r="U211">
+        <v>10000</v>
+      </c>
+      <c r="V211">
+        <v>63</v>
+      </c>
+      <c r="W211">
+        <v>7000</v>
+      </c>
+      <c r="X211">
+        <v>1200000</v>
+      </c>
+      <c r="Y211">
+        <v>14.5</v>
+      </c>
+      <c r="Z211">
+        <v>14</v>
+      </c>
+      <c r="AB211" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC211">
+        <v>37.166699999999999</v>
+      </c>
+      <c r="AD211">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="212" spans="1:30">
+      <c r="A212" t="s">
+        <v>749</v>
+      </c>
+      <c r="B212" t="s">
+        <v>532</v>
+      </c>
+      <c r="C212" t="s">
+        <v>750</v>
+      </c>
+      <c r="D212" t="s">
+        <v>751</v>
+      </c>
+      <c r="E212">
+        <v>45.6</v>
+      </c>
+      <c r="J212">
+        <v>350000</v>
+      </c>
+      <c r="K212">
+        <v>0.7</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212" t="s">
+        <v>407</v>
+      </c>
+      <c r="N212">
+        <v>15</v>
+      </c>
+      <c r="O212" t="s">
+        <v>44</v>
+      </c>
+      <c r="P212">
+        <v>13</v>
+      </c>
+      <c r="Q212">
+        <v>7</v>
+      </c>
+      <c r="R212" t="s">
+        <v>413</v>
+      </c>
+      <c r="S212">
+        <v>19</v>
+      </c>
+      <c r="T212" t="s">
+        <v>408</v>
+      </c>
+      <c r="U212">
+        <v>9800</v>
+      </c>
+      <c r="V212">
+        <v>62</v>
+      </c>
+      <c r="W212">
+        <v>6900</v>
+      </c>
+      <c r="X212">
+        <v>1180000</v>
+      </c>
+      <c r="Y212">
+        <v>14.2</v>
+      </c>
+      <c r="Z212">
+        <v>13</v>
+      </c>
+      <c r="AB212" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC212">
+        <v>37.15</v>
+      </c>
+      <c r="AD212">
+        <v>38.783299999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:30">
+      <c r="A213" t="s">
+        <v>752</v>
+      </c>
+      <c r="B213" t="s">
+        <v>557</v>
+      </c>
+      <c r="C213" t="s">
+        <v>753</v>
+      </c>
+      <c r="D213" t="s">
+        <v>754</v>
+      </c>
+      <c r="E213">
+        <v>43.8</v>
+      </c>
+      <c r="J213">
+        <v>350000</v>
+      </c>
+      <c r="K213">
+        <v>0.8</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213" t="s">
+        <v>407</v>
+      </c>
+      <c r="N213">
+        <v>10</v>
+      </c>
+      <c r="O213" t="s">
+        <v>61</v>
+      </c>
+      <c r="P213">
+        <v>15</v>
+      </c>
+      <c r="Q213">
+        <v>8</v>
+      </c>
+      <c r="R213" t="s">
+        <v>413</v>
+      </c>
+      <c r="S213">
+        <v>18.8</v>
+      </c>
+      <c r="T213" t="s">
+        <v>408</v>
+      </c>
+      <c r="U213">
+        <v>10000</v>
+      </c>
+      <c r="V213">
+        <v>63</v>
+      </c>
+      <c r="W213">
+        <v>7100</v>
+      </c>
+      <c r="X213">
+        <v>1200000</v>
+      </c>
+      <c r="Y213">
+        <v>14.8</v>
+      </c>
+      <c r="Z213">
+        <v>14</v>
+      </c>
+      <c r="AB213" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC213">
+        <v>38.5</v>
+      </c>
+      <c r="AD213">
+        <v>43.416699999999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:30">
+      <c r="A214" t="s">
+        <v>755</v>
+      </c>
+      <c r="B214" t="s">
+        <v>137</v>
+      </c>
+      <c r="C214" t="s">
+        <v>756</v>
+      </c>
+      <c r="D214" t="s">
+        <v>757</v>
+      </c>
+      <c r="E214">
+        <v>52.5</v>
+      </c>
+      <c r="J214">
+        <v>200000</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="s">
+        <v>407</v>
+      </c>
+      <c r="N214">
+        <v>17</v>
+      </c>
+      <c r="O214" t="s">
+        <v>35</v>
+      </c>
+      <c r="P214">
+        <v>15</v>
+      </c>
+      <c r="Q214">
+        <v>11.5</v>
+      </c>
+      <c r="R214" t="s">
+        <v>427</v>
+      </c>
+      <c r="S214">
+        <v>18.5</v>
+      </c>
+      <c r="T214" t="s">
+        <v>408</v>
+      </c>
+      <c r="U214">
+        <v>13000</v>
+      </c>
+      <c r="V214">
+        <v>85</v>
+      </c>
+      <c r="W214">
+        <v>9500</v>
+      </c>
+      <c r="X214">
+        <v>1650000</v>
+      </c>
+      <c r="Y214">
+        <v>17</v>
+      </c>
+      <c r="Z214">
+        <v>15</v>
+      </c>
+      <c r="AB214" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC214">
+        <v>39.883299999999998</v>
+      </c>
+      <c r="AD214">
+        <v>41.25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:30">
+      <c r="A215" t="s">
+        <v>758</v>
+      </c>
+      <c r="B215" t="s">
+        <v>137</v>
+      </c>
+      <c r="C215" t="s">
+        <v>759</v>
+      </c>
+      <c r="D215" t="s">
+        <v>760</v>
+      </c>
+      <c r="E215">
+        <v>53.8</v>
+      </c>
+      <c r="J215">
+        <v>80000</v>
+      </c>
+      <c r="K215">
+        <v>0.8</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215" t="s">
+        <v>407</v>
+      </c>
+      <c r="N215">
+        <v>17</v>
+      </c>
+      <c r="O215" t="s">
+        <v>35</v>
+      </c>
+      <c r="P215">
+        <v>17</v>
+      </c>
+      <c r="Q215">
+        <v>11</v>
+      </c>
+      <c r="R215" t="s">
+        <v>427</v>
+      </c>
+      <c r="S215">
+        <v>18.8</v>
+      </c>
+      <c r="T215" t="s">
+        <v>408</v>
+      </c>
+      <c r="U215">
+        <v>11500</v>
+      </c>
+      <c r="V215">
+        <v>75</v>
+      </c>
+      <c r="W215">
+        <v>8400</v>
+      </c>
+      <c r="X215">
+        <v>1450000</v>
+      </c>
+      <c r="Y215">
+        <v>16.5</v>
+      </c>
+      <c r="Z215">
+        <v>15</v>
+      </c>
+      <c r="AB215" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC215">
+        <v>39.933300000000003</v>
+      </c>
+      <c r="AD215">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:30">
+      <c r="A216" t="s">
+        <v>761</v>
+      </c>
+      <c r="B216" t="s">
+        <v>366</v>
+      </c>
+      <c r="C216" t="s">
+        <v>762</v>
+      </c>
+      <c r="D216" t="s">
+        <v>763</v>
+      </c>
+      <c r="E216">
+        <v>41.5</v>
+      </c>
+      <c r="J216">
+        <v>700000</v>
+      </c>
+      <c r="K216">
+        <v>1.3</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216" t="s">
+        <v>407</v>
+      </c>
+      <c r="N216">
+        <v>9</v>
+      </c>
+      <c r="O216" t="s">
+        <v>54</v>
+      </c>
+      <c r="P216">
+        <v>12</v>
+      </c>
+      <c r="Q216">
+        <v>9.5</v>
+      </c>
+      <c r="R216" t="s">
+        <v>764</v>
+      </c>
+      <c r="S216">
+        <v>18</v>
+      </c>
+      <c r="T216" t="s">
+        <v>408</v>
+      </c>
+      <c r="U216">
+        <v>16000</v>
+      </c>
+      <c r="V216">
+        <v>102</v>
+      </c>
+      <c r="W216">
+        <v>11200</v>
+      </c>
+      <c r="X216">
+        <v>2100000</v>
+      </c>
+      <c r="Y216">
+        <v>19.5</v>
+      </c>
+      <c r="Z216">
+        <v>16</v>
+      </c>
+      <c r="AB216" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC216">
+        <v>37.083300000000001</v>
+      </c>
+      <c r="AD216">
+        <v>37.366700000000002</v>
+      </c>
+    </row>
+    <row r="217" spans="1:30">
+      <c r="A217" t="s">
+        <v>765</v>
+      </c>
+      <c r="B217" t="s">
+        <v>366</v>
+      </c>
+      <c r="C217" t="s">
+        <v>766</v>
+      </c>
+      <c r="D217" t="s">
+        <v>767</v>
+      </c>
+      <c r="E217">
+        <v>44.4</v>
+      </c>
+      <c r="J217">
+        <v>150000</v>
+      </c>
+      <c r="K217">
+        <v>0.8</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217" t="s">
+        <v>407</v>
+      </c>
+      <c r="N217">
+        <v>10</v>
+      </c>
+      <c r="O217" t="s">
+        <v>61</v>
+      </c>
+      <c r="P217">
+        <v>15</v>
+      </c>
+      <c r="Q217">
+        <v>9</v>
+      </c>
+      <c r="R217" t="s">
+        <v>764</v>
+      </c>
+      <c r="S217">
+        <v>18.5</v>
+      </c>
+      <c r="T217" t="s">
+        <v>408</v>
+      </c>
+      <c r="U217">
+        <v>12500</v>
+      </c>
+      <c r="V217">
+        <v>81</v>
+      </c>
+      <c r="W217">
+        <v>9000</v>
+      </c>
+      <c r="X217">
+        <v>1600000</v>
+      </c>
+      <c r="Y217">
+        <v>17.5</v>
+      </c>
+      <c r="Z217">
+        <v>15</v>
+      </c>
+      <c r="AB217" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC217">
+        <v>37.0167</v>
+      </c>
+      <c r="AD217">
+        <v>37.783299999999997</v>
+      </c>
+    </row>
+    <row r="218" spans="1:30">
+      <c r="A218" t="s">
+        <v>768</v>
+      </c>
+      <c r="B218" t="s">
+        <v>366</v>
+      </c>
+      <c r="C218" t="s">
+        <v>769</v>
+      </c>
+      <c r="D218" t="s">
+        <v>770</v>
+      </c>
+      <c r="E218">
+        <v>43.1</v>
+      </c>
+      <c r="J218">
+        <v>65000</v>
+      </c>
+      <c r="K218">
+        <v>0.7</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218" t="s">
+        <v>407</v>
+      </c>
+      <c r="N218">
+        <v>7</v>
+      </c>
+      <c r="O218" t="s">
+        <v>87</v>
+      </c>
+      <c r="P218">
+        <v>16</v>
+      </c>
+      <c r="Q218">
+        <v>9.5</v>
+      </c>
+      <c r="R218" t="s">
+        <v>764</v>
+      </c>
+      <c r="S218">
+        <v>18.5</v>
+      </c>
+      <c r="T218" t="s">
+        <v>408</v>
+      </c>
+      <c r="U218">
+        <v>11000</v>
+      </c>
+      <c r="V218">
+        <v>71</v>
+      </c>
+      <c r="W218">
+        <v>8000</v>
+      </c>
+      <c r="X218">
+        <v>1400000</v>
+      </c>
+      <c r="Y218">
+        <v>17</v>
+      </c>
+      <c r="Z218">
+        <v>15</v>
+      </c>
+      <c r="AB218" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC218">
+        <v>37.033299999999997</v>
+      </c>
+      <c r="AD218">
+        <v>36.633299999999998</v>
+      </c>
+    </row>
+    <row r="219" spans="1:30">
+      <c r="A219" t="s">
+        <v>771</v>
+      </c>
+      <c r="B219" t="s">
+        <v>480</v>
+      </c>
+      <c r="C219" t="s">
+        <v>772</v>
+      </c>
+      <c r="D219" t="s">
+        <v>773</v>
+      </c>
+      <c r="E219">
+        <v>39.6</v>
+      </c>
+      <c r="J219">
+        <v>300000</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219" t="s">
+        <v>407</v>
+      </c>
+      <c r="N219">
+        <v>6</v>
+      </c>
+      <c r="O219" t="s">
+        <v>87</v>
+      </c>
+      <c r="P219">
+        <v>14</v>
+      </c>
+      <c r="Q219">
+        <v>8.5</v>
+      </c>
+      <c r="R219" t="s">
+        <v>78</v>
+      </c>
+      <c r="S219">
+        <v>18</v>
+      </c>
+      <c r="T219" t="s">
+        <v>408</v>
+      </c>
+      <c r="U219">
+        <v>15500</v>
+      </c>
+      <c r="V219">
+        <v>100</v>
+      </c>
+      <c r="W219">
+        <v>11000</v>
+      </c>
+      <c r="X219">
+        <v>2000000</v>
+      </c>
+      <c r="Y219">
+        <v>19</v>
+      </c>
+      <c r="Z219">
+        <v>15</v>
+      </c>
+      <c r="AB219" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC219">
+        <v>37.583300000000001</v>
+      </c>
+      <c r="AD219">
+        <v>36.916699999999999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:30">
+      <c r="A220" t="s">
+        <v>774</v>
+      </c>
+      <c r="B220" t="s">
+        <v>480</v>
+      </c>
+      <c r="C220" t="s">
+        <v>775</v>
+      </c>
+      <c r="D220" t="s">
+        <v>776</v>
+      </c>
+      <c r="E220">
+        <v>43.1</v>
+      </c>
+      <c r="J220">
+        <v>110000</v>
+      </c>
+      <c r="K220">
+        <v>0.7</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+      <c r="M220" t="s">
+        <v>407</v>
+      </c>
+      <c r="N220">
+        <v>7</v>
+      </c>
+      <c r="O220" t="s">
+        <v>87</v>
+      </c>
+      <c r="P220">
+        <v>17</v>
+      </c>
+      <c r="Q220">
+        <v>8.5</v>
+      </c>
+      <c r="R220" t="s">
+        <v>78</v>
+      </c>
+      <c r="S220">
+        <v>18.5</v>
+      </c>
+      <c r="T220" t="s">
+        <v>408</v>
+      </c>
+      <c r="U220">
+        <v>11500</v>
+      </c>
+      <c r="V220">
+        <v>74</v>
+      </c>
+      <c r="W220">
+        <v>8300</v>
+      </c>
+      <c r="X220">
+        <v>1450000</v>
+      </c>
+      <c r="Y220">
+        <v>16.5</v>
+      </c>
+      <c r="Z220">
+        <v>15</v>
+      </c>
+      <c r="AB220" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC220">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AD220">
+        <v>37.183300000000003</v>
+      </c>
+    </row>
+    <row r="221" spans="1:30">
+      <c r="A221" t="s">
+        <v>777</v>
+      </c>
+      <c r="B221" t="s">
+        <v>473</v>
+      </c>
+      <c r="C221" t="s">
+        <v>778</v>
+      </c>
+      <c r="D221" t="s">
+        <v>779</v>
+      </c>
+      <c r="E221">
+        <v>51.2</v>
+      </c>
+      <c r="J221">
+        <v>250000</v>
+      </c>
+      <c r="K221">
+        <v>1.3</v>
+      </c>
+      <c r="L221">
+        <v>16</v>
+      </c>
+      <c r="M221" t="s">
+        <v>34</v>
+      </c>
+      <c r="N221">
+        <v>5</v>
+      </c>
+      <c r="O221" t="s">
+        <v>87</v>
+      </c>
+      <c r="P221">
+        <v>14</v>
+      </c>
+      <c r="Q221">
+        <v>8</v>
+      </c>
+      <c r="R221" t="s">
+        <v>78</v>
+      </c>
+      <c r="S221">
+        <v>17.2</v>
+      </c>
+      <c r="T221" t="s">
+        <v>408</v>
+      </c>
+      <c r="U221">
+        <v>20000</v>
+      </c>
+      <c r="V221">
+        <v>125</v>
+      </c>
+      <c r="W221">
+        <v>13500</v>
+      </c>
+      <c r="X221">
+        <v>2600000</v>
+      </c>
+      <c r="Y221">
+        <v>22.5</v>
+      </c>
+      <c r="Z221">
+        <v>16</v>
+      </c>
+      <c r="AB221" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC221">
+        <v>36.583300000000001</v>
+      </c>
+      <c r="AD221">
+        <v>36.166699999999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:30">
+      <c r="A222" t="s">
+        <v>780</v>
+      </c>
+      <c r="B222" t="s">
+        <v>473</v>
+      </c>
+      <c r="C222" t="s">
+        <v>781</v>
+      </c>
+      <c r="D222" t="s">
+        <v>782</v>
+      </c>
+      <c r="E222">
+        <v>53.6</v>
+      </c>
+      <c r="J222">
+        <v>80000</v>
+      </c>
+      <c r="K222">
+        <v>0.8</v>
+      </c>
+      <c r="L222">
+        <v>16</v>
+      </c>
+      <c r="M222" t="s">
+        <v>34</v>
+      </c>
+      <c r="N222">
+        <v>5</v>
+      </c>
+      <c r="O222" t="s">
+        <v>87</v>
+      </c>
+      <c r="P222">
+        <v>17</v>
+      </c>
+      <c r="Q222">
+        <v>8</v>
+      </c>
+      <c r="R222" t="s">
+        <v>78</v>
+      </c>
+      <c r="S222">
+        <v>17.5</v>
+      </c>
+      <c r="T222" t="s">
+        <v>408</v>
+      </c>
+      <c r="U222">
+        <v>16000</v>
+      </c>
+      <c r="V222">
+        <v>100</v>
+      </c>
+      <c r="W222">
+        <v>11000</v>
+      </c>
+      <c r="X222">
+        <v>2050000</v>
+      </c>
+      <c r="Y222">
+        <v>20</v>
+      </c>
+      <c r="Z222">
+        <v>15</v>
+      </c>
+      <c r="AB222" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC222">
+        <v>36.083300000000001</v>
+      </c>
+      <c r="AD222">
+        <v>35.9833</v>
+      </c>
+    </row>
+    <row r="223" spans="1:30">
+      <c r="A223" t="s">
+        <v>783</v>
+      </c>
+      <c r="B223" t="s">
+        <v>473</v>
+      </c>
+      <c r="C223" t="s">
+        <v>784</v>
+      </c>
+      <c r="D223" t="s">
+        <v>785</v>
+      </c>
+      <c r="E223">
+        <v>50.2</v>
+      </c>
+      <c r="J223">
+        <v>100000</v>
+      </c>
+      <c r="K223">
+        <v>0.9</v>
+      </c>
+      <c r="L223">
+        <v>12</v>
+      </c>
+      <c r="M223" t="s">
+        <v>34</v>
+      </c>
+      <c r="N223">
+        <v>5</v>
+      </c>
+      <c r="O223" t="s">
+        <v>87</v>
+      </c>
+      <c r="P223">
+        <v>16</v>
+      </c>
+      <c r="Q223">
+        <v>8.5</v>
+      </c>
+      <c r="R223" t="s">
+        <v>78</v>
+      </c>
+      <c r="S223">
+        <v>17.8</v>
+      </c>
+      <c r="T223" t="s">
+        <v>408</v>
+      </c>
+      <c r="U223">
+        <v>17000</v>
+      </c>
+      <c r="V223">
+        <v>107</v>
+      </c>
+      <c r="W223">
+        <v>11700</v>
+      </c>
+      <c r="X223">
+        <v>2200000</v>
+      </c>
+      <c r="Y223">
+        <v>21</v>
+      </c>
+      <c r="Z223">
+        <v>15</v>
+      </c>
+      <c r="AB223" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC223">
+        <v>36.833300000000001</v>
+      </c>
+      <c r="AD223">
+        <v>36.2333</v>
+      </c>
+    </row>
+    <row r="224" spans="1:30">
+      <c r="A224" t="s">
+        <v>786</v>
+      </c>
+      <c r="B224" t="s">
+        <v>473</v>
+      </c>
+      <c r="C224" t="s">
+        <v>787</v>
+      </c>
+      <c r="D224" t="s">
+        <v>788</v>
+      </c>
+      <c r="E224">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="J224">
+        <v>85000</v>
+      </c>
+      <c r="K224">
+        <v>0.7</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224" t="s">
+        <v>407</v>
+      </c>
+      <c r="N224">
+        <v>5</v>
+      </c>
+      <c r="O224" t="s">
+        <v>87</v>
+      </c>
+      <c r="P224">
+        <v>16</v>
+      </c>
+      <c r="Q224">
+        <v>8</v>
+      </c>
+      <c r="R224" t="s">
+        <v>78</v>
+      </c>
+      <c r="S224">
+        <v>18</v>
+      </c>
+      <c r="T224" t="s">
+        <v>408</v>
+      </c>
+      <c r="U224">
+        <v>14000</v>
+      </c>
+      <c r="V224">
+        <v>90</v>
+      </c>
+      <c r="W224">
+        <v>10000</v>
+      </c>
+      <c r="X224">
+        <v>1800000</v>
+      </c>
+      <c r="Y224">
+        <v>19</v>
+      </c>
+      <c r="Z224">
+        <v>14</v>
+      </c>
+      <c r="AB224" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC224">
+        <v>36.4833</v>
+      </c>
+      <c r="AD224">
+        <v>36.366700000000002</v>
+      </c>
+    </row>
+    <row r="225" spans="1:30">
+      <c r="A225" t="s">
+        <v>789</v>
+      </c>
+      <c r="B225" t="s">
+        <v>473</v>
+      </c>
+      <c r="C225" t="s">
+        <v>790</v>
+      </c>
+      <c r="D225" t="s">
+        <v>791</v>
+      </c>
+      <c r="E225">
+        <v>39.5</v>
+      </c>
+      <c r="J225">
+        <v>80000</v>
+      </c>
+      <c r="K225">
+        <v>0.7</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225" t="s">
+        <v>407</v>
+      </c>
+      <c r="N225">
+        <v>5</v>
+      </c>
+      <c r="O225" t="s">
+        <v>87</v>
+      </c>
+      <c r="P225">
+        <v>16</v>
+      </c>
+      <c r="Q225">
+        <v>7.5</v>
+      </c>
+      <c r="R225" t="s">
+        <v>78</v>
+      </c>
+      <c r="S225">
+        <v>18.2</v>
+      </c>
+      <c r="T225" t="s">
+        <v>408</v>
+      </c>
+      <c r="U225">
+        <v>13000</v>
+      </c>
+      <c r="V225">
+        <v>84</v>
+      </c>
+      <c r="W225">
+        <v>9300</v>
+      </c>
+      <c r="X225">
+        <v>1650000</v>
+      </c>
+      <c r="Y225">
+        <v>18</v>
+      </c>
+      <c r="Z225">
+        <v>14</v>
+      </c>
+      <c r="AB225" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC225">
+        <v>36.2667</v>
+      </c>
+      <c r="AD225">
+        <v>36.566699999999997</v>
+      </c>
+    </row>
+    <row r="226" spans="1:30">
+      <c r="A226" t="s">
+        <v>792</v>
+      </c>
+      <c r="B226" t="s">
+        <v>793</v>
+      </c>
+      <c r="C226" t="s">
+        <v>64</v>
+      </c>
+      <c r="D226" t="s">
+        <v>794</v>
+      </c>
+      <c r="E226">
+        <v>41.5</v>
+      </c>
+      <c r="J226">
+        <v>250000</v>
+      </c>
+      <c r="K226">
+        <v>0.8</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226" t="s">
+        <v>407</v>
+      </c>
+      <c r="N226">
+        <v>7</v>
+      </c>
+      <c r="O226" t="s">
+        <v>87</v>
+      </c>
+      <c r="P226">
+        <v>15</v>
+      </c>
+      <c r="Q226">
+        <v>8.5</v>
+      </c>
+      <c r="R226" t="s">
+        <v>413</v>
+      </c>
+      <c r="S226">
+        <v>18.5</v>
+      </c>
+      <c r="T226" t="s">
+        <v>408</v>
+      </c>
+      <c r="U226">
+        <v>11000</v>
+      </c>
+      <c r="V226">
+        <v>71</v>
+      </c>
+      <c r="W226">
+        <v>8000</v>
+      </c>
+      <c r="X226">
+        <v>1400000</v>
+      </c>
+      <c r="Y226">
+        <v>16.5</v>
+      </c>
+      <c r="Z226">
+        <v>14</v>
+      </c>
+      <c r="AB226" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC226">
+        <v>37.764800000000001</v>
+      </c>
+      <c r="AD226">
+        <v>38.278599999999997</v>
+      </c>
+    </row>
+    <row r="227" spans="1:30">
+      <c r="A227" t="s">
+        <v>795</v>
+      </c>
+      <c r="B227" t="s">
+        <v>793</v>
+      </c>
+      <c r="C227" t="s">
+        <v>249</v>
+      </c>
+      <c r="D227" t="s">
+        <v>796</v>
+      </c>
+      <c r="E227">
+        <v>45.3</v>
+      </c>
+      <c r="J227">
+        <v>55000</v>
+      </c>
+      <c r="K227">
+        <v>0.6</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227" t="s">
+        <v>407</v>
+      </c>
+      <c r="N227">
+        <v>8</v>
+      </c>
+      <c r="O227" t="s">
+        <v>54</v>
+      </c>
+      <c r="P227">
+        <v>18</v>
+      </c>
+      <c r="Q227">
+        <v>9</v>
+      </c>
+      <c r="R227" t="s">
+        <v>413</v>
+      </c>
+      <c r="S227">
+        <v>18.8</v>
+      </c>
+      <c r="T227" t="s">
+        <v>408</v>
+      </c>
+      <c r="U227">
+        <v>9500</v>
+      </c>
+      <c r="V227">
+        <v>61</v>
+      </c>
+      <c r="W227">
+        <v>6800</v>
+      </c>
+      <c r="X227">
+        <v>1100000</v>
+      </c>
+      <c r="Y227">
+        <v>15</v>
+      </c>
+      <c r="Z227">
+        <v>13</v>
+      </c>
+      <c r="AB227" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC227">
+        <v>37.783299999999997</v>
+      </c>
+      <c r="AD227">
+        <v>37.65</v>
+      </c>
+    </row>
+    <row r="228" spans="1:30">
+      <c r="A228" t="s">
+        <v>797</v>
+      </c>
+      <c r="B228" t="s">
+        <v>506</v>
+      </c>
+      <c r="C228" t="s">
+        <v>798</v>
+      </c>
+      <c r="D228" t="s">
+        <v>799</v>
+      </c>
+      <c r="E228">
+        <v>47.3</v>
+      </c>
+      <c r="J228">
+        <v>200000</v>
+      </c>
+      <c r="K228">
+        <v>0.7</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228" t="s">
+        <v>407</v>
+      </c>
+      <c r="N228">
+        <v>15</v>
+      </c>
+      <c r="O228" t="s">
+        <v>44</v>
+      </c>
+      <c r="P228">
+        <v>15</v>
+      </c>
+      <c r="Q228">
+        <v>7</v>
+      </c>
+      <c r="R228" t="s">
+        <v>413</v>
+      </c>
+      <c r="S228">
+        <v>19</v>
+      </c>
+      <c r="T228" t="s">
+        <v>408</v>
+      </c>
+      <c r="U228">
+        <v>10000</v>
+      </c>
+      <c r="V228">
+        <v>64</v>
+      </c>
+      <c r="W228">
+        <v>7100</v>
+      </c>
+      <c r="X228">
+        <v>1200000</v>
+      </c>
+      <c r="Y228">
+        <v>15</v>
+      </c>
+      <c r="Z228">
+        <v>14</v>
+      </c>
+      <c r="AB228" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC228">
+        <v>37.193300000000001</v>
+      </c>
+      <c r="AD228">
+        <v>40.5867</v>
+      </c>
+    </row>
+    <row r="229" spans="1:30">
+      <c r="A229" t="s">
+        <v>800</v>
+      </c>
+      <c r="B229" t="s">
+        <v>506</v>
+      </c>
+      <c r="C229" t="s">
+        <v>801</v>
+      </c>
+      <c r="D229" t="s">
+        <v>802</v>
+      </c>
+      <c r="E229">
+        <v>49.3</v>
+      </c>
+      <c r="J229">
+        <v>80000</v>
+      </c>
+      <c r="K229">
+        <v>0.9</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229" t="s">
+        <v>407</v>
+      </c>
+      <c r="N229">
+        <v>15</v>
+      </c>
+      <c r="O229" t="s">
+        <v>44</v>
+      </c>
+      <c r="P229">
+        <v>17</v>
+      </c>
+      <c r="Q229">
+        <v>7.5</v>
+      </c>
+      <c r="R229" t="s">
+        <v>413</v>
+      </c>
+      <c r="S229">
+        <v>18.8</v>
+      </c>
+      <c r="T229" t="s">
+        <v>408</v>
+      </c>
+      <c r="U229">
+        <v>11500</v>
+      </c>
+      <c r="V229">
+        <v>73</v>
+      </c>
+      <c r="W229">
+        <v>8200</v>
+      </c>
+      <c r="X229">
+        <v>1400000</v>
+      </c>
+      <c r="Y229">
+        <v>16</v>
+      </c>
+      <c r="Z229">
+        <v>15</v>
+      </c>
+      <c r="AB229" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC229">
+        <v>37.416699999999999</v>
+      </c>
+      <c r="AD229">
+        <v>41.333300000000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:30">
+      <c r="A230" t="s">
+        <v>803</v>
+      </c>
+      <c r="B230" t="s">
+        <v>506</v>
+      </c>
+      <c r="C230" t="s">
+        <v>804</v>
+      </c>
+      <c r="D230" t="s">
+        <v>805</v>
+      </c>
+      <c r="E230">
+        <v>47.3</v>
+      </c>
+      <c r="J230">
+        <v>100000</v>
+      </c>
+      <c r="K230">
+        <v>0.6</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230" t="s">
+        <v>407</v>
+      </c>
+      <c r="N230">
+        <v>15</v>
+      </c>
+      <c r="O230" t="s">
+        <v>44</v>
+      </c>
+      <c r="P230">
+        <v>15</v>
+      </c>
+      <c r="Q230">
+        <v>7</v>
+      </c>
+      <c r="R230" t="s">
+        <v>413</v>
+      </c>
+      <c r="S230">
+        <v>19.2</v>
+      </c>
+      <c r="T230" t="s">
+        <v>408</v>
+      </c>
+      <c r="U230">
+        <v>9000</v>
+      </c>
+      <c r="V230">
+        <v>57</v>
+      </c>
+      <c r="W230">
+        <v>6400</v>
+      </c>
+      <c r="X230">
+        <v>980000</v>
+      </c>
+      <c r="Y230">
+        <v>14</v>
+      </c>
+      <c r="Z230">
+        <v>13</v>
+      </c>
+      <c r="AB230" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC230">
+        <v>37.066699999999997</v>
+      </c>
+      <c r="AD230">
+        <v>41.216700000000003</v>
       </c>
     </row>
   </sheetData>
@@ -18517,51 +22212,51 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>678</v>
+        <v>806</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>679</v>
+        <v>807</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>680</v>
+        <v>808</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>681</v>
+        <v>809</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>682</v>
+        <v>810</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>683</v>
+        <v>811</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>684</v>
+        <v>812</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>685</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="55.2" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>686</v>
+        <v>814</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>687</v>
+        <v>815</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>688</v>
+        <v>816</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>690</v>
+        <v>818</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>691</v>
+        <v>819</v>
       </c>
       <c r="H2" s="2">
         <v>3</v>
@@ -18569,25 +22264,25 @@
     </row>
     <row r="3" spans="1:8" ht="41.4" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>692</v>
+        <v>820</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>693</v>
+        <v>821</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>694</v>
+        <v>822</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>695</v>
+        <v>823</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>696</v>
+        <v>824</v>
       </c>
       <c r="H3" s="2">
         <v>3</v>
@@ -18595,25 +22290,25 @@
     </row>
     <row r="4" spans="1:8" ht="55.2" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>697</v>
+        <v>825</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>698</v>
+        <v>826</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>699</v>
+        <v>827</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>700</v>
+        <v>828</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>701</v>
+        <v>829</v>
       </c>
       <c r="H4" s="2">
         <v>3</v>
@@ -18621,25 +22316,25 @@
     </row>
     <row r="5" spans="1:8" ht="55.2" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>702</v>
+        <v>830</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>703</v>
+        <v>831</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>704</v>
+        <v>832</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>705</v>
+        <v>833</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>706</v>
+        <v>834</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
@@ -18647,25 +22342,25 @@
     </row>
     <row r="6" spans="1:8" ht="69" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>707</v>
+        <v>835</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>708</v>
+        <v>836</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>709</v>
+        <v>837</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>710</v>
+        <v>838</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>711</v>
+        <v>839</v>
       </c>
       <c r="H6" s="2">
         <v>3</v>
@@ -18673,25 +22368,25 @@
     </row>
     <row r="7" spans="1:8" ht="69" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>712</v>
+        <v>840</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>713</v>
+        <v>841</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>714</v>
+        <v>842</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>715</v>
+        <v>843</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>716</v>
+        <v>844</v>
       </c>
       <c r="H7" s="2">
         <v>3</v>
@@ -18716,74 +22411,74 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>717</v>
+        <v>845</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>718</v>
+        <v>846</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>719</v>
+        <v>847</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>720</v>
+        <v>848</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>721</v>
+        <v>849</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>722</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>723</v>
+        <v>851</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>724</v>
+        <v>852</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>725</v>
+        <v>853</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>726</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>727</v>
+        <v>855</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>728</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>729</v>
+        <v>857</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>730</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>729</v>
+        <v>857</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>731</v>
+        <v>859</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>732</v>
+        <v>860</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>733</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -18807,16 +22502,16 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.6" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>678</v>
+        <v>806</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>679</v>
+        <v>807</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>734</v>
+        <v>862</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>681</v>
+        <v>809</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
@@ -18826,15 +22521,15 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>735</v>
+        <v>863</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>686</v>
+        <v>814</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>687</v>
+        <v>815</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -18858,10 +22553,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>692</v>
+        <v>820</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>693</v>
+        <v>821</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
@@ -18885,10 +22580,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>697</v>
+        <v>825</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>698</v>
+        <v>826</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -18912,10 +22607,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>702</v>
+        <v>830</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>703</v>
+        <v>831</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -18939,10 +22634,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>707</v>
+        <v>835</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>708</v>
+        <v>836</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -18966,10 +22661,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>712</v>
+        <v>840</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>713</v>
+        <v>841</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
